--- a/data/trans_dic/P79A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79A_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,67</t>
+          <t>3,65; 8,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,24</t>
+          <t>2,03; 4,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,79</t>
+          <t>3,06; 5,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,94</t>
+          <t>1,66; 3,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,11</t>
+          <t>1,81; 3,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,73</t>
+          <t>1,9; 2,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,78</t>
+          <t>0,33; 1,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,17</t>
+          <t>0,25; 1,16</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,84</t>
+          <t>1,86; 3,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,71</t>
+          <t>1,81; 2,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,47</t>
+          <t>1,95; 2,78</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>56449</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16056; 34360</t>
+          <t>21094; 50192</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16098; 32055</t>
+          <t>16660; 34990</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34607; 60793</t>
+          <t>42880; 74652</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46236</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92254</t>
+          <t>104714</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28410; 67444</t>
+          <t>36958; 71977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30612; 69507</t>
+          <t>39252; 72283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67348; 123438</t>
+          <t>83568; 130693</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>8478</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6428</t>
+          <t>0; 7280</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1896; 11742</t>
+          <t>2392; 14192</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3142; 15297</t>
+          <t>3651; 16726</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52053; 98092</t>
+          <t>65370; 111975</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56186; 99043</t>
+          <t>67493; 104829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114847; 175348</t>
+          <t>141544; 201772</t>
         </is>
       </c>
     </row>
